--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,124 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>109958250</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56693</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>582395</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7055729</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -3093,7 +3093,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117642166</v>
+        <v>117640171</v>
       </c>
       <c r="B23" t="n">
         <v>57287</v>
@@ -3129,7 +3129,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582213</v>
+        <v>582252</v>
       </c>
       <c r="R23" t="n">
-        <v>7055683</v>
+        <v>7055936</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3322,7 +3322,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117640171</v>
+        <v>117642166</v>
       </c>
       <c r="B25" t="n">
         <v>57287</v>
@@ -3358,7 +3358,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582252</v>
+        <v>582213</v>
       </c>
       <c r="R25" t="n">
-        <v>7055936</v>
+        <v>7055683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117702841</v>
+        <v>117703761</v>
       </c>
       <c r="B26" t="n">
-        <v>97753</v>
+        <v>57440</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3451,38 +3451,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582304</v>
+        <v>582384</v>
       </c>
       <c r="R26" t="n">
-        <v>7055627</v>
+        <v>7055672</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3524,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3667,10 +3672,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117703353</v>
+        <v>117703581</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3679,30 +3684,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3711,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582336</v>
+        <v>582380</v>
       </c>
       <c r="R28" t="n">
-        <v>7055634</v>
+        <v>7055594</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,7 +3752,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3756,7 +3762,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3789,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117702753</v>
+        <v>117702841</v>
       </c>
       <c r="B29" t="n">
-        <v>97857</v>
+        <v>97753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3799,21 +3805,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3823,10 +3829,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582288</v>
+        <v>582304</v>
       </c>
       <c r="R29" t="n">
-        <v>7055644</v>
+        <v>7055627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3864,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3874,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3901,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117703581</v>
+        <v>117702753</v>
       </c>
       <c r="B30" t="n">
-        <v>57287</v>
+        <v>97857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,43 +3913,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582380</v>
+        <v>582288</v>
       </c>
       <c r="R30" t="n">
-        <v>7055594</v>
+        <v>7055644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3976,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3986,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4012,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117703610</v>
+        <v>117703353</v>
       </c>
       <c r="B31" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,31 +4025,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4057,10 +4057,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582376</v>
+        <v>582336</v>
       </c>
       <c r="R31" t="n">
-        <v>7055601</v>
+        <v>7055634</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117703761</v>
+        <v>117703610</v>
       </c>
       <c r="B32" t="n">
-        <v>57440</v>
+        <v>57287</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4145,27 +4145,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582384</v>
+        <v>582376</v>
       </c>
       <c r="R32" t="n">
-        <v>7055672</v>
+        <v>7055601</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4209,7 +4209,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -3093,10 +3093,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117640171</v>
+        <v>117642166</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3138,10 +3138,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582252</v>
+        <v>582213</v>
       </c>
       <c r="R23" t="n">
-        <v>7055936</v>
+        <v>7055683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,7 +3213,7 @@
         <v>117641076</v>
       </c>
       <c r="B24" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117642166</v>
+        <v>117640171</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582213</v>
+        <v>582252</v>
       </c>
       <c r="R25" t="n">
-        <v>7055683</v>
+        <v>7055936</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,10 +3439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117703761</v>
+        <v>117703581</v>
       </c>
       <c r="B26" t="n">
-        <v>57440</v>
+        <v>57288</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,27 +3455,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582384</v>
+        <v>582380</v>
       </c>
       <c r="R26" t="n">
-        <v>7055672</v>
+        <v>7055594</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117703505</v>
+        <v>117702841</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>97755</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,42 +3568,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582361</v>
+        <v>582304</v>
       </c>
       <c r="R27" t="n">
-        <v>7055596</v>
+        <v>7055627</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3635,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3645,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,10 +3668,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117703581</v>
+        <v>117703353</v>
       </c>
       <c r="B28" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3684,31 +3680,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3717,10 +3712,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582380</v>
+        <v>582336</v>
       </c>
       <c r="R28" t="n">
-        <v>7055594</v>
+        <v>7055634</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3752,7 +3747,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3762,7 +3757,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,10 +3784,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117702841</v>
+        <v>117702942</v>
       </c>
       <c r="B29" t="n">
-        <v>97753</v>
+        <v>57288</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,38 +3796,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582304</v>
+        <v>582310</v>
       </c>
       <c r="R29" t="n">
-        <v>7055627</v>
+        <v>7055625</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3862,19 +3862,9 @@
           <t>2024-06-11</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117702753</v>
+        <v>117703761</v>
       </c>
       <c r="B30" t="n">
-        <v>97857</v>
+        <v>57441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,38 +3903,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582288</v>
+        <v>582384</v>
       </c>
       <c r="R30" t="n">
-        <v>7055644</v>
+        <v>7055672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3976,7 +3971,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3986,7 +3981,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +4008,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117703353</v>
+        <v>117702753</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>97859</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,42 +4020,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Taråberget (Taråberget), Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582336</v>
+        <v>582288</v>
       </c>
       <c r="R31" t="n">
-        <v>7055634</v>
+        <v>7055644</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4092,7 +4083,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4102,7 +4093,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4132,7 +4123,7 @@
         <v>117703610</v>
       </c>
       <c r="B32" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4246,10 +4237,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117702942</v>
+        <v>117703505</v>
       </c>
       <c r="B33" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4258,31 +4249,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4291,10 +4281,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582310</v>
+        <v>582361</v>
       </c>
       <c r="R33" t="n">
-        <v>7055625</v>
+        <v>7055596</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4324,9 +4314,19 @@
           <t>2024-06-11</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4351,6 +4351,122 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121497021</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>582208</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7055929</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>födosök</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4356,7 +4356,7 @@
         <v>121497021</v>
       </c>
       <c r="B34" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4356,7 +4356,7 @@
         <v>121497021</v>
       </c>
       <c r="B34" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4356,7 +4356,7 @@
         <v>121497021</v>
       </c>
       <c r="B34" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4356,7 +4356,7 @@
         <v>121497021</v>
       </c>
       <c r="B34" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4467,6 +4467,127 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125262384</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57624</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>582225</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7055878</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4472,7 +4472,7 @@
         <v>125262384</v>
       </c>
       <c r="B35" t="n">
-        <v>57624</v>
+        <v>57738</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4472,12 +4472,7 @@
         <v>125262384</v>
       </c>
       <c r="B35" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57755</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4583,6 +4583,123 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127761445</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>582299</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7055651</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på äldre tall, högt upp</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4588,7 +4588,7 @@
         <v>127761445</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4588,7 +4588,7 @@
         <v>127761445</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4588,7 +4588,7 @@
         <v>127761445</v>
       </c>
       <c r="B36" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4588,7 +4588,7 @@
         <v>127761445</v>
       </c>
       <c r="B36" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4700,6 +4700,117 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128642599</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98572</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>582195</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7055929</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4705,7 +4705,7 @@
         <v>128642599</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -4923,7 +4923,7 @@
         <v>133933066</v>
       </c>
       <c r="B39" t="n">
-        <v>91971</v>
+        <v>91978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109835391</v>
+        <v>109954074</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582318.3240102943</v>
+        <v>582390</v>
       </c>
       <c r="R2" t="n">
-        <v>7055676.953135424</v>
+        <v>7055747</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -746,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109954045</v>
+        <v>109954223</v>
       </c>
       <c r="B3" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582393.2173966174</v>
+        <v>582381</v>
       </c>
       <c r="R3" t="n">
-        <v>7055743.860724417</v>
+        <v>7055773</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109954223</v>
+        <v>117640047</v>
       </c>
       <c r="B4" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,29 +911,28 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582380.8786717399</v>
+        <v>582267</v>
       </c>
       <c r="R4" t="n">
-        <v>7055772.9057546</v>
+        <v>7055947</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +956,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,37 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109954410</v>
+        <v>109954440</v>
       </c>
       <c r="B5" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582363.7290292341</v>
+        <v>582360</v>
       </c>
       <c r="R5" t="n">
-        <v>7055781.358702273</v>
+        <v>7055787</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1090,7 +1069,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1079,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109957699</v>
+        <v>109955558</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582382.9979755546</v>
+        <v>582209</v>
       </c>
       <c r="R6" t="n">
-        <v>7055605.661349648</v>
+        <v>7055706</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1202,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109958496</v>
+        <v>117641076</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,43 +1225,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582395.3913204318</v>
+        <v>582240</v>
       </c>
       <c r="R7" t="n">
-        <v>7055728.789313032</v>
+        <v>7055941</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1279,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,68 +1309,58 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109953845</v>
+        <v>109954045</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582393.7084276102</v>
+        <v>582394</v>
       </c>
       <c r="R8" t="n">
-        <v>7055707.833313996</v>
+        <v>7055744</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1439,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,54 +1429,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109955599</v>
+        <v>133933066</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Taråberget, Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582206.5946732371</v>
+        <v>582302</v>
       </c>
       <c r="R9" t="n">
-        <v>7055707.424096552</v>
+        <v>7055677</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,22 +1494,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,27 +1514,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109957678</v>
+        <v>109957392</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>582382.9979755546</v>
+        <v>582354</v>
       </c>
       <c r="R10" t="n">
-        <v>7055605.661349648</v>
+        <v>7055577</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,56 +1634,46 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109958250</v>
+        <v>109957283</v>
       </c>
       <c r="B11" t="n">
-        <v>57147</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100011</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>582396</v>
+        <v>582354</v>
       </c>
       <c r="R11" t="n">
-        <v>7055729</v>
+        <v>7055577</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1783,7 +1705,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1715,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,59 +1742,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109955609</v>
+        <v>109954410</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>582209.7574431244</v>
+        <v>582364</v>
       </c>
       <c r="R12" t="n">
-        <v>7055705.726363516</v>
+        <v>7055782</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,7 +1813,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1823,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,49 +1838,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109954074</v>
+        <v>109957285</v>
       </c>
       <c r="B13" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1979,13 +1886,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>582389.9967683166</v>
+        <v>582354</v>
       </c>
       <c r="R13" t="n">
-        <v>7055747.781441296</v>
+        <v>7055577</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2014,7 +1921,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +1931,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,49 +1946,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109955558</v>
+        <v>109957699</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2092,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582209.7574431244</v>
+        <v>582383</v>
       </c>
       <c r="R14" t="n">
-        <v>7055705.726363516</v>
+        <v>7055606</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2127,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,71 +2054,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114081743</v>
+        <v>114081388</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>582408</v>
+        <v>582320</v>
       </c>
       <c r="R15" t="n">
-        <v>7055604</v>
+        <v>7055629</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2245,7 +2137,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2147,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,59 +2174,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114081462</v>
+        <v>114081486</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582346</v>
+        <v>582336</v>
       </c>
       <c r="R16" t="n">
-        <v>7055635</v>
+        <v>7055641</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2363,7 +2245,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2255,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,16 +2285,11 @@
         <v>114081680</v>
       </c>
       <c r="B17" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2437,7 +2314,7 @@
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2513,15 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114081388</v>
+        <v>109835391</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,38 +2401,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>582320</v>
+        <v>582318</v>
       </c>
       <c r="R18" t="n">
-        <v>7055629</v>
+        <v>7055677</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2584,22 +2456,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,15 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114081161</v>
+        <v>109957678</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,43 +2509,38 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>582287</v>
+        <v>582383</v>
       </c>
       <c r="R19" t="n">
-        <v>7055637</v>
+        <v>7055606</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,22 +2564,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,27 +2594,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114081486</v>
+        <v>109958250</v>
       </c>
       <c r="B20" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,35 +2617,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100011</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>582336</v>
+        <v>582396</v>
       </c>
       <c r="R20" t="n">
-        <v>7055641</v>
+        <v>7055729</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2815,22 +2677,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,77 +2707,66 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114176809</v>
+        <v>109953845</v>
       </c>
       <c r="B21" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>582176</v>
+        <v>582394</v>
       </c>
       <c r="R21" t="n">
-        <v>7055760</v>
+        <v>7055708</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2939,22 +2790,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,32 +2832,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114174050</v>
+        <v>109955609</v>
       </c>
       <c r="B22" t="n">
-        <v>56470</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3014,15 +2860,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3031,13 +2873,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582209</v>
+        <v>582210</v>
       </c>
       <c r="R22" t="n">
         <v>7055706</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3061,12 +2903,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-06-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,44 +2933,39 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117640171</v>
+        <v>117640766</v>
       </c>
       <c r="B23" t="n">
-        <v>57288</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3129,19 +2976,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>582252</v>
+        <v>582237</v>
       </c>
       <c r="R23" t="n">
-        <v>7055936</v>
+        <v>7055957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3173,7 +3020,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3183,7 +3030,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3210,15 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117642166</v>
+        <v>109958496</v>
       </c>
       <c r="B24" t="n">
-        <v>57288</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3244,24 +3086,25 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>582213</v>
+        <v>582396</v>
       </c>
       <c r="R24" t="n">
-        <v>7055683</v>
+        <v>7055729</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3285,22 +3128,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2023-06-10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,27 +3158,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117641076</v>
+        <v>114081161</v>
       </c>
       <c r="B25" t="n">
-        <v>90501</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3343,34 +3181,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582240</v>
+        <v>582287</v>
       </c>
       <c r="R25" t="n">
-        <v>7055941</v>
+        <v>7055637</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3397,22 +3241,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,15 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117703761</v>
+        <v>114081462</v>
       </c>
       <c r="B26" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3455,39 +3294,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582384</v>
+        <v>582346</v>
       </c>
       <c r="R26" t="n">
-        <v>7055672</v>
+        <v>7055635</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3514,22 +3354,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,57 +3396,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117703505</v>
+        <v>114081743</v>
       </c>
       <c r="B27" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>582361</v>
+        <v>582408</v>
       </c>
       <c r="R27" t="n">
-        <v>7055596</v>
+        <v>7055604</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3630,22 +3467,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3672,50 +3509,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117702753</v>
+        <v>117640171</v>
       </c>
       <c r="B28" t="n">
-        <v>97861</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>582288</v>
+        <v>582252</v>
       </c>
       <c r="R28" t="n">
-        <v>7055644</v>
+        <v>7055936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3742,22 +3579,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3784,15 +3621,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117703610</v>
+        <v>117641260</v>
       </c>
       <c r="B29" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,19 +3652,19 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>582376</v>
+        <v>582244</v>
       </c>
       <c r="R29" t="n">
-        <v>7055601</v>
+        <v>7055943</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,22 +3691,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3901,50 +3733,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117702841</v>
+        <v>117642166</v>
       </c>
       <c r="B30" t="n">
-        <v>97757</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>582304</v>
+        <v>582213</v>
       </c>
       <c r="R30" t="n">
-        <v>7055627</v>
+        <v>7055683</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3971,22 +3803,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,15 +3845,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117703581</v>
+        <v>117702942</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,19 +3876,19 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>582380</v>
+        <v>582310</v>
       </c>
       <c r="R31" t="n">
-        <v>7055594</v>
+        <v>7055625</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,19 +3918,9 @@
           <t>2024-06-11</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-06-11</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4130,15 +3947,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117702942</v>
+        <v>117703581</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4166,19 +3978,19 @@
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>582310</v>
+        <v>582380</v>
       </c>
       <c r="R32" t="n">
-        <v>7055625</v>
+        <v>7055594</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4208,9 +4020,19 @@
           <t>2024-06-11</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4237,54 +4059,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117703353</v>
+        <v>117703610</v>
       </c>
       <c r="B33" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Taråberget (Taråberget), Ång</t>
+          <t>Taråberget, Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>582336</v>
+        <v>582376</v>
       </c>
       <c r="R33" t="n">
-        <v>7055634</v>
+        <v>7055601</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4316,7 +4134,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4326,7 +4144,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4356,12 +4174,7 @@
         <v>121497021</v>
       </c>
       <c r="B34" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4469,27 +4282,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125262384</v>
+        <v>127761445</v>
       </c>
       <c r="B35" t="n">
-        <v>57755</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4497,14 +4310,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>i par</t>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4513,10 +4322,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>582225</v>
+        <v>582299</v>
       </c>
       <c r="R35" t="n">
-        <v>7055878</v>
+        <v>7055651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4543,22 +4352,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på äldre tall, högt upp</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4585,10 +4399,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127761445</v>
+        <v>128644145</v>
       </c>
       <c r="B36" t="n">
-        <v>57685</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,10 +4439,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>582299</v>
+        <v>582364</v>
       </c>
       <c r="R36" t="n">
-        <v>7055651</v>
+        <v>7055815</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4655,27 +4469,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på äldre tall, högt upp</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4690,49 +4504,50 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128642599</v>
+        <v>133933598</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4741,13 +4556,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>582195</v>
+        <v>582299</v>
       </c>
       <c r="R37" t="n">
-        <v>7055929</v>
+        <v>7055680</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4771,22 +4586,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bohål m kammare, 4.5cm i diameter. 2,5m ovan mark i asp. Ytterligare ett äldre bohål på 5 m höjd.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4801,39 +4611,39 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133933598</v>
+        <v>114174050</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4841,25 +4651,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582299</v>
+        <v>582209</v>
       </c>
       <c r="R38" t="n">
-        <v>7055680</v>
+        <v>7055706</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4883,17 +4698,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bohål m kammare, 4.5cm i diameter. 2,5m ovan mark i asp. Ytterligare ett äldre bohål på 5 m höjd.</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,60 +4718,72 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133933066</v>
+        <v>114176809</v>
       </c>
       <c r="B39" t="n">
-        <v>91978</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Taråberget, Taråberget, Ång</t>
+          <t>Taråberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>582302</v>
+        <v>582176</v>
       </c>
       <c r="R39" t="n">
-        <v>7055677</v>
+        <v>7055760</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4985,12 +4807,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5005,15 +4837,1023 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>117703761</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>582384</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7055672</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127723786</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>582219</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7055741</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125262384</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>582225</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7055878</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127723712</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>582213</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7055734</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>117702841</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>582304</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7055627</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117703353</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>582336</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7055634</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117703505</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>582361</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7055596</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128642599</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>582195</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7055929</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>117702753</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Taråberget, Taråberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>582288</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7055644</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20312-2022 artfynd.xlsx
+++ b/artfynd/A 20312-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109954074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109954223</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117640047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109954440</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109955558</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117641076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109954045</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133933066</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109957392</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109957283</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109954410</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1955,6 +2015,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109957285</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109957699</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081388</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2279,6 +2354,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081486</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081680</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2495,6 +2580,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109835391</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109957678</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2716,6 +2811,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109958250</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2829,6 +2929,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109953845</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2942,6 +3047,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109955609</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3054,6 +3164,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117640766</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3167,6 +3282,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109958496</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3280,6 +3400,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081161</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3393,6 +3518,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081462</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3506,6 +3636,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114081743</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3618,6 +3753,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117640171</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3730,6 +3870,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117641260</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3842,6 +3987,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117642166</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3944,6 +4094,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117702942</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4056,6 +4211,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117703581</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4168,6 +4328,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117703610</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4279,6 +4444,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497021</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4396,6 +4566,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127761445</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4513,6 +4688,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128644145</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4620,6 +4800,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133933598</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4727,6 +4912,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114174050</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4846,6 +5036,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114176809</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4958,6 +5153,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117703761</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5079,6 +5279,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723786</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5195,6 +5400,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125262384</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5307,6 +5517,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723712</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5414,6 +5629,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117702841</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5525,6 +5745,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117703353</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5636,6 +5861,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117703505</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5747,6 +5977,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128642599</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5854,8 +6089,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117702753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>